--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="445">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-diagnostic-report-document</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -628,6 +628,9 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
+    <t>final</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -657,7 +660,7 @@
 </t>
   </si>
   <si>
-    <t>Service category</t>
+    <t>Type de résultat</t>
   </si>
   <si>
     <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
@@ -666,13 +669,16 @@
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="18748-4"/&gt;
+    &lt;display value="Imagerie"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -786,11 +792,8 @@
 Effective TimeOccurrence</t>
   </si>
   <si>
-    <t>dateTime
-Period</t>
-  </si>
-  <si>
-    <t>Clinically relevant time/time-period for report</t>
+    <t xml:space="preserve">dateTime
+</t>
   </si>
   <si>
     <t>The time or time-period the observed values are related to. When the subject of the report is a patient, this is usually either the time of the procedure or of specimen collection(s), but very often the source of the date/time is not known, only the date/time itself.</t>
@@ -853,11 +856,11 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document)
 </t>
   </si>
   <si>
-    <t>Responsible Diagnostic Service</t>
+    <t>Exécutant</t>
   </si>
   <si>
     <t>The diagnostic service that is responsible for issuing the report.</t>
@@ -901,7 +904,7 @@
 Reported by</t>
   </si>
   <si>
-    <t>Primary result interpreter</t>
+    <t>Auteur</t>
   </si>
   <si>
     <t>The practitioner or organization that is responsible for the report's conclusions and interpretations.</t>
@@ -1200,46 +1203,46 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-result-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-laboratory-report-results-document)
+</t>
+  </si>
+  <si>
+    <t>Résultats d'examen (actuels ou antérieurs)</t>
+  </si>
+  <si>
+    <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
+  </si>
+  <si>
+    <t>Les résultats sont exprimés sous forme non codée dans notre cas d’usage. Le contenu narratif du résultat est porté dans une note</t>
+  </si>
+  <si>
+    <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:reference}
+</t>
+  </si>
+  <si>
+    <t>OBXs</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=COMP].target</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:resultatActuel</t>
+  </si>
+  <si>
+    <t>resultatActuel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-result-document)
 </t>
   </si>
   <si>
-    <t>Résultats d'examen (actuels ou antérieurs)</t>
-  </si>
-  <si>
-    <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
-  </si>
-  <si>
-    <t>Les résultats sont exprimés sous forme non codée dans notre cas d’usage. Le contenu narratif du résultat est porté dans une note</t>
-  </si>
-  <si>
-    <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:reference}
-</t>
-  </si>
-  <si>
-    <t>OBXs</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:resultatActuel</t>
-  </si>
-  <si>
-    <t>resultatActuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1)
-</t>
-  </si>
-  <si>
     <t>Résultats actuels de l'examen d'imagerie</t>
   </si>
   <si>
-    <t>Observations can contain observations.</t>
+    <t>Si les résultats d'examen sont codés, ils sont référencés dans FRObservationResultDocument. Si les résultats d'examen sont exprimés sous forme non codée, ils sont portés dans une note de FRObservationResultDocument.</t>
   </si>
   <si>
     <t>DiagnosticReport.result:resultatAnterieur</t>
@@ -1281,7 +1284,7 @@
 </t>
   </si>
   <si>
-    <t>Key images associated with this report</t>
+    <t>Images clés associées à ce rapport</t>
   </si>
   <si>
     <t>A list of key images associated with this report. The images are generally created during the diagnostic process, and may be directly of the patient, or of treated specimens (i.e. slides of interest).</t>
@@ -1343,11 +1346,11 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-media-document)
 </t>
   </si>
   <si>
-    <t>Reference to the image source</t>
+    <t>Lien vers les images clés</t>
   </si>
   <si>
     <t>Reference to the image source.</t>
@@ -1387,6 +1390,9 @@
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
@@ -1403,7 +1409,7 @@
 </t>
   </si>
   <si>
-    <t>Entire report as issued</t>
+    <t>Copie du document</t>
   </si>
   <si>
     <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
@@ -3262,7 +3268,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>164</v>
       </c>
@@ -3281,7 +3287,7 @@
         <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3610,7 +3616,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>190</v>
       </c>
@@ -3629,7 +3635,7 @@
         <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>91</v>
@@ -3658,7 +3664,7 @@
         <v>80</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>80</v>
@@ -3673,13 +3679,13 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
         <v>192</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3712,38 +3718,38 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>80</v>
@@ -3752,16 +3758,16 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3772,7 +3778,7 @@
         <v>80</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>80</v>
@@ -3787,11 +3793,9 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
         <v>208</v>
       </c>
@@ -3811,7 +3815,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3866,7 +3870,7 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>214</v>
@@ -3899,7 +3903,7 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
@@ -4178,7 +4182,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>242</v>
       </c>
@@ -4191,13 +4195,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
@@ -4209,16 +4213,16 @@
         <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4282,28 +4286,28 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4322,19 +4326,19 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4383,7 +4387,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4401,25 +4405,25 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4438,19 +4442,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4497,7 +4501,7 @@
         <v>139</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4512,30 +4516,30 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AN24" t="s" s="2">
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>273</v>
       </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
+      <c r="B25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="B25" t="s" s="2">
+      <c r="D25" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4545,7 +4549,7 @@
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
@@ -4554,19 +4558,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="M25" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4615,7 +4619,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4630,28 +4634,28 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4670,19 +4674,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4731,7 +4735,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4746,24 +4750,24 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4786,13 +4790,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4843,7 +4847,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4864,7 +4868,7 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4872,10 +4876,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4946,7 +4950,7 @@
         <v>138</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
@@ -4955,7 +4959,7 @@
         <v>139</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4984,13 +4988,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
@@ -5012,13 +5016,13 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5069,7 +5073,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5098,10 +5102,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5124,13 +5128,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5181,7 +5185,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5202,7 +5206,7 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5210,10 +5214,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5221,7 +5225,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>79</v>
@@ -5284,7 +5288,7 @@
         <v>138</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>80</v>
@@ -5293,7 +5297,7 @@
         <v>139</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5322,13 +5326,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>80</v>
@@ -5407,7 +5411,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5436,10 +5440,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5462,13 +5466,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5519,7 +5523,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5540,7 +5544,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5548,10 +5552,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5622,7 +5626,7 @@
         <v>138</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
@@ -5631,7 +5635,7 @@
         <v>139</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5660,10 +5664,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5689,13 +5693,13 @@
         <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5703,7 +5707,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>80</v>
@@ -5745,7 +5749,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>90</v>
@@ -5774,10 +5778,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5803,10 +5807,10 @@
         <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5818,7 +5822,7 @@
         <v>80</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>80</v>
@@ -5833,29 +5837,29 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5884,13 +5888,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>80</v>
@@ -5915,7 +5919,7 @@
         <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
         <v>137</v>
@@ -5969,7 +5973,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5998,10 +6002,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6024,13 +6028,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6081,7 +6085,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6102,7 +6106,7 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6110,10 +6114,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6184,7 +6188,7 @@
         <v>138</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
@@ -6193,7 +6197,7 @@
         <v>139</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6222,10 +6226,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6251,13 +6255,13 @@
         <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6265,7 +6269,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>80</v>
@@ -6307,7 +6311,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>90</v>
@@ -6336,10 +6340,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6362,13 +6366,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6419,7 +6423,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6448,13 +6452,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>80</v>
@@ -6533,7 +6537,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6562,10 +6566,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6588,13 +6592,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6645,7 +6649,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6666,7 +6670,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -6674,10 +6678,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6748,7 +6752,7 @@
         <v>138</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>80</v>
@@ -6757,7 +6761,7 @@
         <v>139</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6786,10 +6790,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6815,13 +6819,13 @@
         <v>104</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6829,7 +6833,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>80</v>
@@ -6871,7 +6875,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>90</v>
@@ -6900,10 +6904,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6926,13 +6930,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6983,7 +6987,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7012,10 +7016,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7041,13 +7045,13 @@
         <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7055,7 +7059,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>80</v>
@@ -7097,7 +7101,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>90</v>
@@ -7126,10 +7130,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7152,13 +7156,13 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7209,7 +7213,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7238,10 +7242,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7264,16 +7268,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7323,7 +7327,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7332,7 +7336,7 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
@@ -7352,10 +7356,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7381,13 +7385,13 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7413,31 +7417,31 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7466,10 +7470,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7495,13 +7499,13 @@
         <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7551,7 +7555,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7572,7 +7576,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -7580,10 +7584,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7606,16 +7610,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7665,7 +7669,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7694,10 +7698,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7720,19 +7724,19 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -7781,7 +7785,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7799,7 +7803,7 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>229</v>
@@ -7810,18 +7814,18 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>79</v>
@@ -7836,19 +7840,19 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -7885,7 +7889,7 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -7895,7 +7899,7 @@
         <v>139</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7913,27 +7917,27 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AN54" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
+      <c r="B55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="B55" t="s" s="2">
+      <c r="D55" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7943,7 +7947,7 @@
         <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
@@ -7952,19 +7956,19 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="O55" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8013,7 +8017,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8031,27 +8035,27 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="B56" t="s" s="2">
+      <c r="D56" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="D56" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8061,7 +8065,7 @@
         <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -8070,19 +8074,19 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8135,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8149,10 +8153,10 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8160,10 +8164,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8186,16 +8190,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8245,7 +8249,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8266,22 +8270,22 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN57" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8291,7 +8295,7 @@
         <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>80</v>
@@ -8300,17 +8304,17 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
@@ -8359,7 +8363,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8377,10 +8381,10 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8388,10 +8392,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8414,13 +8418,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8471,7 +8475,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8492,7 +8496,7 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -8500,10 +8504,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8529,10 +8533,10 @@
         <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>161</v>
@@ -8585,7 +8589,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8606,7 +8610,7 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
@@ -8614,14 +8618,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8643,10 +8647,10 @@
         <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>161</v>
@@ -8701,7 +8705,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8730,10 +8734,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8756,19 +8760,19 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -8817,7 +8821,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8838,18 +8842,18 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN62" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8863,7 +8867,7 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>80</v>
@@ -8872,13 +8876,13 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8929,7 +8933,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -8950,7 +8954,7 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>80</v>
@@ -8958,14 +8962,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8984,17 +8988,17 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9043,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9061,10 +9065,10 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>80</v>
@@ -9072,10 +9076,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9098,13 +9102,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9131,7 +9135,7 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>206</v>
+        <v>434</v>
       </c>
       <c r="Y65" t="s" s="2">
         <v>435</v>
@@ -9155,7 +9159,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9173,7 +9177,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>437</v>
@@ -9182,7 +9186,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>438</v>
       </c>
@@ -9195,13 +9199,13 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>80</v>
@@ -9289,7 +9293,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>444</v>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
